--- a/Manufacturing/Gerbers/Required_impedance_control.xlsx
+++ b/Manufacturing/Gerbers/Required_impedance_control.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexandershort/Repos/Soft-Services/Leonhart/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexandershort/Repos/Soft-Services/Leonhart/Manufacturing/Gerbers/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{5E12DFD7-BD56-C54A-938E-1D51B7D279C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="7" r:id="rId1"/>
